--- a/hira_material_automation/output/monthly/202601_202607__nonmetal_anchor__040019__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__nonmetal_anchor__040019__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-04T22:02:25</t>
+          <t>2026-07-14T22:02:17</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>b157f521be83f8cad71f70e29550e3087e88488ea7f2d1b47a77a36d2055540e</t>
+          <t>ec614813ca35b97aa70dca569c0b2147b5ba4e99643e7124dbb72f4732787ff5</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202607__nonmetal_anchor__040019__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__nonmetal_anchor__040019__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-14T22:02:17</t>
+          <t>2026-07-24T22:09:11</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ec614813ca35b97aa70dca569c0b2147b5ba4e99643e7124dbb72f4732787ff5</t>
+          <t>44ec0592a2a40a5dad19b0b25421864de5e0f93a787cd3313f7c5fd3998b8e5f</t>
         </is>
       </c>
     </row>
